--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,36 +419,24 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-01/2025-07-29</t>
+          <t>Ventas 2025-07-01 / 2025-07-30</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Venue Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gross Sales</t>
-        </is>
-      </c>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Net Sales</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Discounts</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Voids</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Bill Count</t>
@@ -458,21 +446,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#001 Florida Mall Orlando FL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>93928.94</v>
-      </c>
+          <t>Barcelona 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>93928.94</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>201180.61</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>0</v>
       </c>
@@ -480,21 +462,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#002 American Dream Mall NJ</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>81407.27</v>
-      </c>
+          <t>Barcelona 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>81407.27</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>90395.28999999999</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>0</v>
       </c>
@@ -502,21 +478,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#003 Sawgrass Mills Mall FL</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>110972.24</v>
-      </c>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>110972.24</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>31238.35</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>0</v>
       </c>
@@ -524,21 +494,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#004 Weston Town Center FL</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>66065.32000000001</v>
-      </c>
+          <t>Málaga 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>66065.32000000001</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
+        <v>116208.14</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>0</v>
       </c>
@@ -546,21 +510,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#005 Vineland Orlando FL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>23416.72</v>
-      </c>
+          <t>Málaga 3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23416.72</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
+        <v>48826.63</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -568,21 +526,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#006 Aventura, FL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>31687.16</v>
-      </c>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>31687.16</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
+        <v>136221.15</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>0</v>
       </c>
@@ -590,21 +542,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REPORT SUMMARY (6 entries)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>407477.65</v>
-      </c>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>407477.65</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
+        <v>135490.57</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>0</v>
       </c>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-07-01 / 2025-07-30</t>
+          <t>Ventas 2025-07-01 / 2025-07-31</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>201180.61</v>
+        <v>207531.29</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>90395.28999999999</v>
+        <v>93178.38</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>31238.35</v>
+        <v>32376.31</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>116208.14</v>
+        <v>120125.59</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>48826.63</v>
+        <v>50437.09</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>136221.15</v>
+        <v>141710.6</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>135490.57</v>
+        <v>139532.93</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-07-01 / 2025-07-31</t>
+          <t>Ventas 2025-08-01 / 2025-08-01</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>207531.29</v>
+        <v>7457.74</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>93178.38</v>
+        <v>3077</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>32376.31</v>
+        <v>1643.14</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>120125.59</v>
+        <v>4409.14</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>50437.09</v>
+        <v>1770.67</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>141710.6</v>
+        <v>5634.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>139532.93</v>
+        <v>4838.68</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-01</t>
+          <t>Ventas 2025-08-01 / 2025-08-02</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>7457.74</v>
+        <v>16092.24</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3077</v>
+        <v>6771.27</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1643.14</v>
+        <v>3599.59</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>4409.14</v>
+        <v>8959.139999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1770.67</v>
+        <v>3755.82</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>5634.82</v>
+        <v>10111.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>4838.68</v>
+        <v>10279.89</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-02</t>
+          <t>Ventas 2025-08-01 / 2025-08-03</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>16092.24</v>
+        <v>23525.96</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6771.27</v>
+        <v>10902.86</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3599.59</v>
+        <v>5169.27</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>8959.139999999999</v>
+        <v>13007.14</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3755.82</v>
+        <v>5696.68</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>10111.55</v>
+        <v>15355.33</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>10279.89</v>
+        <v>15270.33</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-03</t>
+          <t>Ventas 2025-08-01 / 2025-08-04</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>23525.96</v>
+        <v>30536.69</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>10902.86</v>
+        <v>13927.77</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5169.27</v>
+        <v>6386.68</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>13007.14</v>
+        <v>17121.23</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5696.68</v>
+        <v>7543.37</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>15355.33</v>
+        <v>20059.87</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>15270.33</v>
+        <v>20018.18</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-04</t>
+          <t>Ventas 2025-08-01 / 2025-08-05</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>30536.69</v>
+        <v>37530.19</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>13927.77</v>
+        <v>17080.73</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6386.68</v>
+        <v>7773</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>17121.23</v>
+        <v>21338.77</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>7543.37</v>
+        <v>9215.24</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>20059.87</v>
+        <v>24840.87</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>20018.18</v>
+        <v>24915.09</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-05</t>
+          <t>Ventas 2025-08-01 / 2025-08-06</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>37530.19</v>
+        <v>44058.07</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>17080.73</v>
+        <v>19940.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>7773</v>
+        <v>8959.41</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>21338.77</v>
+        <v>25486.73</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>9215.24</v>
+        <v>11003.35</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>24840.87</v>
+        <v>29045.87</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>24915.09</v>
+        <v>29355.29</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-06</t>
+          <t>Ventas 2025-08-01 / 2025-08-07</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>44058.07</v>
+        <v>51329.35</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>19940.59</v>
+        <v>23124.32</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>8959.41</v>
+        <v>10180.45</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>25486.73</v>
+        <v>29942.32</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>11003.35</v>
+        <v>12885.43</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>29045.87</v>
+        <v>33693.15</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>29355.29</v>
+        <v>33561.32</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-07</t>
+          <t>Ventas 2025-08-01 / 2025-08-08</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>51329.35</v>
+        <v>59174.35</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>23124.32</v>
+        <v>26376.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>10180.45</v>
+        <v>11729.73</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>29942.32</v>
+        <v>34621.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>12885.43</v>
+        <v>14534.29</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>33693.15</v>
+        <v>37942.05</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>33561.32</v>
+        <v>38953.89</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-08</t>
+          <t>Ventas 2025-08-01 / 2025-08-09</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>59174.35</v>
+        <v>67802.3</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>26376.59</v>
+        <v>29664.36</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>11729.73</v>
+        <v>13590</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>34621.36</v>
+        <v>39336.55</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>14534.29</v>
+        <v>16467.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>37942.05</v>
+        <v>42247.87</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>38953.89</v>
+        <v>45426.53</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-09</t>
+          <t>Ventas 2025-08-01 / 2025-08-10</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>67802.3</v>
+        <v>75353.57000000001</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>29664.36</v>
+        <v>33302.82</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>13590</v>
+        <v>15169.09</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>39336.55</v>
+        <v>43372.77</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>16467.45</v>
+        <v>18351.18</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>42247.87</v>
+        <v>46391.15</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>45426.53</v>
+        <v>50190.85</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-10</t>
+          <t>Ventas 2025-08-01 / 2025-08-11</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>75353.57000000001</v>
+        <v>83051.44</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>33302.82</v>
+        <v>36178.55</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15169.09</v>
+        <v>16810.85</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>43372.77</v>
+        <v>47879.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>18351.18</v>
+        <v>19891</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>46391.15</v>
+        <v>50652.33</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>50190.85</v>
+        <v>54584.61</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-11</t>
+          <t>Ventas 2025-08-01 / 2025-08-12</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>83051.44</v>
+        <v>90499.48</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>36178.55</v>
+        <v>39157.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>16810.85</v>
+        <v>18406.37</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>47879.09</v>
+        <v>52563.6</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>19891</v>
+        <v>21670.51</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>50652.33</v>
+        <v>55974.42</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>54584.61</v>
+        <v>58939.72</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-12</t>
+          <t>Ventas 2025-08-01 / 2025-08-13</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>90499.48</v>
+        <v>97086.67</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>39157.09</v>
+        <v>42170.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>18406.37</v>
+        <v>20040.69</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>52563.6</v>
+        <v>56892.33</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>21670.51</v>
+        <v>23289.74</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>55974.42</v>
+        <v>60674.6</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>58939.72</v>
+        <v>63158.55</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-13</t>
+          <t>Ventas 2025-08-01 / 2025-08-14</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>97086.67</v>
+        <v>104220.04</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>42170.64</v>
+        <v>44818.18</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>20040.69</v>
+        <v>21894.65</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>56892.33</v>
+        <v>61389.65</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23289.74</v>
+        <v>25068.74</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>60674.6</v>
+        <v>65506.05</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>63158.55</v>
+        <v>67499.86</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-14</t>
+          <t>Ventas 2025-08-01 / 2025-08-15</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>104220.04</v>
+        <v>112145.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>44818.18</v>
+        <v>48207.27</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>21894.65</v>
+        <v>24354.92</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>61389.65</v>
+        <v>67199.33</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>25068.74</v>
+        <v>26915.78</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>65506.05</v>
+        <v>70748.24000000001</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>67499.86</v>
+        <v>73142.17</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-15</t>
+          <t>Ventas 2025-08-01 / 2025-08-16</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>112145.36</v>
+        <v>120128.73</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>48207.27</v>
+        <v>51776.77</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>24354.92</v>
+        <v>26379.05</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>67199.33</v>
+        <v>72607.50999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>26915.78</v>
+        <v>28430.89</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>70748.24000000001</v>
+        <v>75653.50999999999</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>73142.17</v>
+        <v>78513.25999999999</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-16</t>
+          <t>Ventas 2025-08-01 / 2025-08-17</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>120128.73</v>
+        <v>127004.05</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>51776.77</v>
+        <v>54853.05</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>26379.05</v>
+        <v>27747.51</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>72607.50999999999</v>
+        <v>77549.14999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>28430.89</v>
+        <v>30107.74</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>75653.50999999999</v>
+        <v>80406.60000000001</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>78513.25999999999</v>
+        <v>83279.45</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-17</t>
+          <t>Ventas 2025-08-01 / 2025-08-18</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>127004.05</v>
+        <v>133532.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>54853.05</v>
+        <v>57334.41</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>27747.51</v>
+        <v>29162.87</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>77549.14999999999</v>
+        <v>81596.19</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>30107.74</v>
+        <v>31628.69</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>80406.60000000001</v>
+        <v>85499.42</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>83279.45</v>
+        <v>87226.03</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-18</t>
+          <t>Ventas 2025-08-01 / 2025-08-19</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>133532.27</v>
+        <v>140253.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>57334.41</v>
+        <v>60133.14</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>29162.87</v>
+        <v>30653.73</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>81596.19</v>
+        <v>86406.33</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>31628.69</v>
+        <v>33660.63</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>85499.42</v>
+        <v>89727.60000000001</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>87226.03</v>
+        <v>92126.49000000001</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-19</t>
+          <t>Ventas 2025-08-01 / 2025-08-20</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>140253.36</v>
+        <v>145968.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>60133.14</v>
+        <v>62919.36</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>30653.73</v>
+        <v>32010.14</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>86406.33</v>
+        <v>91025.42</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>33660.63</v>
+        <v>35498.76</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>89727.60000000001</v>
+        <v>94389.16</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>92126.49000000001</v>
+        <v>96624.89</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-20</t>
+          <t>Ventas 2025-08-01 / 2025-08-21</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>145968.27</v>
+        <v>152588.64</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>62919.36</v>
+        <v>65437.68</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>32010.14</v>
+        <v>33313.18</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>91025.42</v>
+        <v>95573.78</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>35498.76</v>
+        <v>37042.63</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>94389.16</v>
+        <v>99285.28999999999</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>96624.89</v>
+        <v>101199.78</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-21</t>
+          <t>Ventas 2025-08-01 / 2025-08-22</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>152588.64</v>
+        <v>159135.91</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>65437.68</v>
+        <v>67855.88</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>33313.18</v>
+        <v>35245.73</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>95573.78</v>
+        <v>100356.4</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>37042.63</v>
+        <v>38536.74</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>99285.28999999999</v>
+        <v>103991.11</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>101199.78</v>
+        <v>106335.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-22</t>
+          <t>Ventas 2025-08-01 / 2025-08-23</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>159135.91</v>
+        <v>166823.32</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>67855.88</v>
+        <v>70545.28999999999</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>35245.73</v>
+        <v>37506.41</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>100356.4</v>
+        <v>105033.46</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>38536.74</v>
+        <v>40427.01</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>103991.11</v>
+        <v>108484.65</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>106335.41</v>
+        <v>112285.63</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-23</t>
+          <t>Ventas 2025-08-01 / 2025-08-24</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>166823.32</v>
+        <v>174185.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>70545.28999999999</v>
+        <v>73450.95</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>37506.41</v>
+        <v>39204.5</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>105033.46</v>
+        <v>109345.37</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>40427.01</v>
+        <v>41970.51</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>108484.65</v>
+        <v>112646.38</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>112285.63</v>
+        <v>117145.27</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-24</t>
+          <t>Ventas 2025-08-01 / 2025-08-25</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>174185.27</v>
+        <v>180637.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>73450.95</v>
+        <v>76076.57000000001</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>39204.5</v>
+        <v>40385.29</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>109345.37</v>
+        <v>113728.01</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>41970.51</v>
+        <v>43537.01</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>112646.38</v>
+        <v>116772.65</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>117145.27</v>
+        <v>121725.9</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-25</t>
+          <t>Ventas 2025-08-01 / 2025-08-26</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>180637.45</v>
+        <v>186895.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>76076.57000000001</v>
+        <v>78372.77</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>40385.29</v>
+        <v>41627.29</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>113728.01</v>
+        <v>117471.42</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>43537.01</v>
+        <v>45308.96</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>116772.65</v>
+        <v>120841.2</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>121725.9</v>
+        <v>126192.56</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-26</t>
+          <t>Ventas 2025-08-01 / 2025-08-27</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>186895.95</v>
+        <v>193006.49</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>78372.77</v>
+        <v>80744.08</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>41627.29</v>
+        <v>42734.47</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>117471.42</v>
+        <v>121057.1</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>45308.96</v>
+        <v>46818.15</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>120841.2</v>
+        <v>125087.02</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>126192.56</v>
+        <v>130204.85</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-27</t>
+          <t>Ventas 2025-08-01 / 2025-08-28</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>193006.49</v>
+        <v>198344.9</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>80744.08</v>
+        <v>83013.58</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>42734.47</v>
+        <v>43938.61</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>121057.1</v>
+        <v>124765.46</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>46818.15</v>
+        <v>48159.21</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>125087.02</v>
+        <v>129781.2</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>130204.85</v>
+        <v>134180.82</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-28</t>
+          <t>Ventas 2025-08-01 / 2025-08-29</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>198344.9</v>
+        <v>205466.54</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>83013.58</v>
+        <v>85516.72</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>43938.61</v>
+        <v>45475.15</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>124765.46</v>
+        <v>128797.83</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>48159.21</v>
+        <v>49581.71</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>129781.2</v>
+        <v>134568.75</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>134180.82</v>
+        <v>139027.09</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-29</t>
+          <t>Ventas 2025-08-01 / 2025-08-30</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>205466.54</v>
+        <v>213167.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>85516.72</v>
+        <v>88323.84</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>45475.15</v>
+        <v>47346.11</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>128797.83</v>
+        <v>132958.78</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>49581.71</v>
+        <v>51139.02</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>134568.75</v>
+        <v>138960.38</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>139027.09</v>
+        <v>144684.14</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-30</t>
+          <t>Ventas 2025-08-01 / 2025-08-31</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>213167.95</v>
+        <v>220153.22</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>88323.84</v>
+        <v>91388.10000000001</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>47346.11</v>
+        <v>48694.02</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>132958.78</v>
+        <v>136323.37</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>51139.02</v>
+        <v>52740.65</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>138960.38</v>
+        <v>143057.2</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>144684.14</v>
+        <v>149492.63</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-01 / 2025-08-31</t>
+          <t>Ventas 2025-09-01 / 2025-09-01</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>220153.22</v>
+        <v>5543.73</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>91388.10000000001</v>
+        <v>2105.82</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>48694.02</v>
+        <v>612.5</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>136323.37</v>
+        <v>3005.41</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>52740.65</v>
+        <v>1511.78</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>143057.2</v>
+        <v>3400.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>149492.63</v>
+        <v>3618.45</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-01</t>
+          <t>Ventas 2025-09-01 / 2025-09-02</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>5543.73</v>
+        <v>11108.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2105.82</v>
+        <v>4147.53</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>612.5</v>
+        <v>1547.77</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>3005.41</v>
+        <v>6047.59</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1511.78</v>
+        <v>2427.88</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3400.73</v>
+        <v>6878.27</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>3618.45</v>
+        <v>7585.5</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-02</t>
+          <t>Ventas 2025-09-01 / 2025-09-03</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>11108.23</v>
+        <v>16701.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4147.53</v>
+        <v>6124.03</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1547.77</v>
+        <v>2450.15</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6047.59</v>
+        <v>9183.27</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2427.88</v>
+        <v>3323.53</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>6878.27</v>
+        <v>10435.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>7585.5</v>
+        <v>11509.15</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-03</t>
+          <t>Ventas 2025-09-01 / 2025-09-04</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>16701.36</v>
+        <v>22043.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6124.03</v>
+        <v>8411.84</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2450.15</v>
+        <v>3483.56</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>9183.27</v>
+        <v>12299.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3323.53</v>
+        <v>4185.18</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>10435.64</v>
+        <v>14177.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>11509.15</v>
+        <v>15431.22</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-04</t>
+          <t>Ventas 2025-09-01 / 2025-09-05</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>22043.09</v>
+        <v>28227.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>8411.84</v>
+        <v>11047.7</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3483.56</v>
+        <v>4973.61</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>12299.64</v>
+        <v>15770.82</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4185.18</v>
+        <v>5238.46</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>14177.18</v>
+        <v>18299.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>15431.22</v>
+        <v>19861.75</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-05</t>
+          <t>Ventas 2025-09-01 / 2025-09-06</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>28227.36</v>
+        <v>35215.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>11047.7</v>
+        <v>14084.01</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4973.61</v>
+        <v>6847.08</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>15770.82</v>
+        <v>20194.84</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5238.46</v>
+        <v>7141.78</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>18299.73</v>
+        <v>23551.27</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>19861.75</v>
+        <v>25287.1</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-06</t>
+          <t>Ventas 2025-09-01 / 2025-09-07</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>35215.95</v>
+        <v>41771.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>14084.01</v>
+        <v>17019.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6847.08</v>
+        <v>7989.45</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>20194.84</v>
+        <v>23415.93</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>7141.78</v>
+        <v>8560.870000000001</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>23551.27</v>
+        <v>28559.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>25287.1</v>
+        <v>29418.45</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-07</t>
+          <t>Ventas 2025-09-01 / 2025-09-08</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>41771.45</v>
+        <v>45939.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>17019.09</v>
+        <v>19004.35</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>7989.45</v>
+        <v>9044.809999999999</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>23415.93</v>
+        <v>26547.65</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>8560.870000000001</v>
+        <v>9753.92</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>28559.55</v>
+        <v>32253.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>29418.45</v>
+        <v>32480.86</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-08</t>
+          <t>Ventas 2025-09-01 / 2025-09-09</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>45939.55</v>
+        <v>50576.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>19004.35</v>
+        <v>20735.76</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9044.809999999999</v>
+        <v>9839.040000000001</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>26547.65</v>
+        <v>29166.2</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>9753.92</v>
+        <v>10894.66</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>32253.09</v>
+        <v>36105.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>32480.86</v>
+        <v>35144.72</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-09</t>
+          <t>Ventas 2025-09-01 / 2025-09-10</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>50576.27</v>
+        <v>56038.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>20735.76</v>
+        <v>22699.04</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9839.040000000001</v>
+        <v>10655.49</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>29166.2</v>
+        <v>31985.15</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>10894.66</v>
+        <v>11758.75</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>36105.64</v>
+        <v>38841.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>35144.72</v>
+        <v>38603.9</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-10</t>
+          <t>Ventas 2025-09-01 / 2025-09-11</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>56038.45</v>
+        <v>61492.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>22699.04</v>
+        <v>25452.17</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>10655.49</v>
+        <v>11571.4</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>31985.15</v>
+        <v>34546.11</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>11758.75</v>
+        <v>12573.72</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>38841.09</v>
+        <v>43475.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>38603.9</v>
+        <v>42430.45</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>

--- a/Acumulado_interanual.xlsx
+++ b/Acumulado_interanual.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-11</t>
+          <t>Ventas 2025-09-01 / 2025-09-12</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>61492.68</v>
+        <v>66788.17999999999</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>25452.17</v>
+        <v>27601.4</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>11571.4</v>
+        <v>12797.67</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>34546.11</v>
+        <v>38050.02</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>12573.72</v>
+        <v>13412.72</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>43475.18</v>
+        <v>48280.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>42430.45</v>
+        <v>47254.57</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
